--- a/docs/Mapping_casi_uso/matrimoni/Matr_001.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_001.xlsx
@@ -803,7 +803,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -812,7 +812,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -821,7 +821,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -830,7 +830,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -839,13 +839,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -854,7 +854,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -863,13 +863,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -878,7 +878,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Interprete</t>
@@ -989,13 +989,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1099,7 +1099,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9617,10 +9617,10 @@
         <v>261</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>262</v>
@@ -10261,10 +10261,10 @@
         <v>264</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>265</v>
@@ -10905,10 +10905,10 @@
         <v>267</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>268</v>
@@ -11549,10 +11549,10 @@
         <v>270</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>271</v>
@@ -12193,10 +12193,10 @@
         <v>273</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D483" s="2" t="s">
         <v>274</v>
@@ -12837,10 +12837,10 @@
         <v>276</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>274</v>
@@ -13642,10 +13642,10 @@
         <v>281</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D546" s="2" t="s">
         <v>282</v>
@@ -14286,10 +14286,10 @@
         <v>284</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>282</v>
@@ -15471,7 +15471,7 @@
         <v>326</v>
       </c>
       <c r="F625" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G625" s="2" t="s">
         <v>58</v>
